--- a/Ice Dance Medals Wiki.xlsx
+++ b/Ice Dance Medals Wiki.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulinareina/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paulinareina/Desktop/Career Exploration Stuff/Data Science Training/The Data Incubator/The Data Incubator Onboarding/Streamlit/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCA3F08E-E364-4F43-A272-CAFFD816AFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732D2AB9-1AD2-7648-BF9E-3C0CD96D2232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16300" xr2:uid="{79483C13-5B93-B744-8781-585329BF415F}"/>
+    <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16300" xr2:uid="{79483C13-5B93-B744-8781-585329BF415F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="81">
   <si>
     <t>Games</t>
   </si>
@@ -1620,6 +1619,27 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>2026 Milano Cortina</t>
+  </si>
+  <si>
+    <t>and Guillaume Cizeron (FRA)</t>
+  </si>
+  <si>
+    <t>Madison Chock</t>
+  </si>
+  <si>
+    <t>and Evan Bates (USA)</t>
+  </si>
+  <si>
+    <t>Piper Giles</t>
+  </si>
+  <si>
+    <t>and Paul Poirier (CAN)</t>
+  </si>
+  <si>
+    <t>Laurence Fournier Beaudry</t>
   </si>
 </sst>
 </file>
@@ -4399,8 +4419,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5405CDF1-67A4-9D42-A13F-E241EA74E4F3}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="6" width="36.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -4778,6 +4801,34 @@
       </c>
       <c r="D27" s="3" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="18" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
